--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_110/per_file_predictions_epoch_110.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run7/epoch_110/per_file_predictions_epoch_110.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.8390,0.0466,0.0504,0.0147</t>
-  </si>
-  <si>
-    <t>0.0126,0.0027,0.0020,0.9919</t>
-  </si>
-  <si>
-    <t>0.7902,0.0085,0.0010,0.2151</t>
-  </si>
-  <si>
-    <t>0.4713,0.0007,0.0008,0.7914</t>
-  </si>
-  <si>
-    <t>0.9966,0.0021,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9953,0.0046,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9730,0.0219,0.0046,0.0019</t>
-  </si>
-  <si>
-    <t>0.9916,0.0017,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.9888,0.0119,0.0019,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0024,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.4142,0.1989,0.4263,0.0085</t>
-  </si>
-  <si>
-    <t>0.1919,0.0183,0.8743,0.0005</t>
-  </si>
-  <si>
-    <t>0.7063,0.0023,0.5973,0.0005</t>
-  </si>
-  <si>
-    <t>0.1389,0.0576,0.8281,0.0030</t>
-  </si>
-  <si>
-    <t>0.7853,0.1113,0.0998,0.0046</t>
-  </si>
-  <si>
-    <t>0.0427,0.9586,0.0034,0.0007</t>
-  </si>
-  <si>
-    <t>0.0219,0.9775,0.0017,0.0004</t>
-  </si>
-  <si>
-    <t>0.5551,0.6644,0.0034,0.0007</t>
-  </si>
-  <si>
-    <t>0.0773,0.9449,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.0906,0.9313,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.3913,0.0152,0.6756,0.0134</t>
-  </si>
-  <si>
-    <t>0.3162,0.0347,0.6190,0.0734</t>
-  </si>
-  <si>
-    <t>0.0392,0.0264,0.9426,0.0102</t>
-  </si>
-  <si>
-    <t>0.2891,0.0355,0.7131,0.0066</t>
-  </si>
-  <si>
-    <t>0.4269,0.0059,0.7589,0.0056</t>
-  </si>
-  <si>
-    <t>0.0746,0.0051,0.9330,0.0048</t>
-  </si>
-  <si>
-    <t>0.0090,0.0021,0.9946,0.0001</t>
-  </si>
-  <si>
-    <t>0.4776,0.6671,0.0046,0.0040</t>
-  </si>
-  <si>
-    <t>0.5233,0.0683,0.5044,0.0155</t>
-  </si>
-  <si>
-    <t>0.0016,0.0075,0.9922,0.0015</t>
-  </si>
-  <si>
-    <t>0.1298,0.5183,0.3358,0.0022</t>
-  </si>
-  <si>
-    <t>0.7215,0.1794,0.0914,0.0197</t>
-  </si>
-  <si>
-    <t>0.0198,0.0940,0.9627,0.0010</t>
-  </si>
-  <si>
-    <t>0.6616,0.5463,0.0065,0.0012</t>
-  </si>
-  <si>
-    <t>0.0049,0.9811,0.0739,0.0038</t>
-  </si>
-  <si>
-    <t>0.0339,0.5215,0.3524,0.1159</t>
-  </si>
-  <si>
-    <t>0.2204,0.0160,0.7955,0.0174</t>
-  </si>
-  <si>
-    <t>0.2301,0.0207,0.7693,0.0182</t>
-  </si>
-  <si>
-    <t>0.2439,0.0222,0.4897,0.2132</t>
-  </si>
-  <si>
-    <t>0.0042,0.1921,0.9628,0.0003</t>
-  </si>
-  <si>
-    <t>0.0022,0.9896,0.0031,0.0000</t>
-  </si>
-  <si>
-    <t>0.0068,0.1454,0.9621,0.0022</t>
-  </si>
-  <si>
-    <t>0.1436,0.5215,0.0151,0.5194</t>
-  </si>
-  <si>
-    <t>0.0036,0.9791,0.0418,0.0107</t>
-  </si>
-  <si>
-    <t>0.0132,0.9635,0.0348,0.0010</t>
-  </si>
-  <si>
-    <t>0.0044,0.9780,0.0651,0.0077</t>
-  </si>
-  <si>
-    <t>0.0060,0.1419,0.9700,0.0025</t>
-  </si>
-  <si>
-    <t>0.0014,0.0719,0.9938,0.0001</t>
-  </si>
-  <si>
-    <t>0.0826,0.1475,0.7221,0.0038</t>
-  </si>
-  <si>
-    <t>0.0152,0.0015,0.9776,0.0061</t>
-  </si>
-  <si>
-    <t>0.0030,0.0067,0.9872,0.0040</t>
-  </si>
-  <si>
-    <t>0.0053,0.0234,0.9884,0.0008</t>
-  </si>
-  <si>
-    <t>0.8331,0.2568,0.0045,0.0013</t>
-  </si>
-  <si>
-    <t>0.9913,0.0052,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9740,0.0242,0.0023,0.0018</t>
-  </si>
-  <si>
-    <t>0.0223,0.0349,0.9589,0.0010</t>
-  </si>
-  <si>
-    <t>0.9945,0.0037,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9956,0.0043,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.6113,0.5443,0.0021,0.0007</t>
-  </si>
-  <si>
-    <t>0.0026,0.7832,0.9494,0.0012</t>
-  </si>
-  <si>
-    <t>0.0025,0.0203,0.9765,0.0119</t>
-  </si>
-  <si>
-    <t>0.0023,0.0310,0.9894,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.9482,0.9674,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0033,0.9962,0.0010</t>
-  </si>
-  <si>
-    <t>0.0286,0.9193,0.0541,0.0010</t>
-  </si>
-  <si>
-    <t>0.0047,0.9931,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.8117,0.0165,0.2854,0.0033</t>
-  </si>
-  <si>
-    <t>0.6793,0.1102,0.3016,0.0053</t>
-  </si>
-  <si>
-    <t>0.0263,0.1286,0.8831,0.0003</t>
-  </si>
-  <si>
-    <t>0.0039,0.7853,0.7353,0.0008</t>
-  </si>
-  <si>
-    <t>0.0041,0.8576,0.6651,0.0003</t>
-  </si>
-  <si>
-    <t>0.0020,0.9620,0.2844,0.0006</t>
-  </si>
-  <si>
-    <t>0.0027,0.9098,0.5020,0.0005</t>
-  </si>
-  <si>
-    <t>0.0723,0.0006,0.0174,0.9359</t>
-  </si>
-  <si>
-    <t>0.0038,0.0015,0.0002,0.9979</t>
-  </si>
-  <si>
-    <t>0.0059,0.0029,0.0003,0.9967</t>
-  </si>
-  <si>
-    <t>0.0075,0.0032,0.0005,0.9961</t>
-  </si>
-  <si>
-    <t>0.0166,0.0045,0.0265,0.9796</t>
-  </si>
-  <si>
-    <t>0.0428,0.0026,0.0050,0.9773</t>
-  </si>
-  <si>
-    <t>0.0006,0.9750,0.8361,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.8178,0.9789,0.0001</t>
-  </si>
-  <si>
-    <t>0.0067,0.4172,0.8061,0.0006</t>
-  </si>
-  <si>
-    <t>0.0014,0.7852,0.9097,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.9671,0.3792,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9090,0.6211,0.0000</t>
-  </si>
-  <si>
-    <t>0.9917,0.0046,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9800,0.0181,0.0037,0.0005</t>
-  </si>
-  <si>
-    <t>0.9504,0.0492,0.0073,0.0019</t>
-  </si>
-  <si>
-    <t>0.9948,0.0010,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9929,0.0031,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9937,0.0032,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.9804,0.0298,0.0012,0.0003</t>
-  </si>
-  <si>
-    <t>0.9638,0.0531,0.0032,0.0003</t>
-  </si>
-  <si>
-    <t>0.9930,0.0006,0.0002,0.0023</t>
-  </si>
-  <si>
-    <t>0.9929,0.0073,0.0011,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9952,0.0006,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9959,0.0031,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9958,0.0017,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0009,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.0622,0.0028,0.9774,0.0004</t>
-  </si>
-  <si>
-    <t>0.0151,0.0168,0.9770,0.0007</t>
-  </si>
-  <si>
-    <t>0.4424,0.0189,0.6820,0.0062</t>
-  </si>
-  <si>
-    <t>0.1129,0.0419,0.8431,0.0035</t>
-  </si>
-  <si>
-    <t>0.0654,0.9283,0.0035,0.0034</t>
-  </si>
-  <si>
-    <t>0.0189,0.9732,0.0021,0.0015</t>
-  </si>
-  <si>
-    <t>0.0116,0.9751,0.0013,0.0073</t>
-  </si>
-  <si>
-    <t>0.6045,0.5427,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.1977,0.8425,0.0058,0.0022</t>
-  </si>
-  <si>
-    <t>0.0263,0.9675,0.0013,0.0009</t>
-  </si>
-  <si>
-    <t>0.9377,0.0895,0.0053,0.0005</t>
-  </si>
-  <si>
-    <t>0.8063,0.0231,0.2071,0.0110</t>
-  </si>
-  <si>
-    <t>0.1572,0.0361,0.8299,0.0031</t>
-  </si>
-  <si>
-    <t>0.1332,0.6874,0.0552,0.1594</t>
-  </si>
-  <si>
-    <t>0.4891,0.0646,0.4256,0.1160</t>
-  </si>
-  <si>
-    <t>0.0702,0.6541,0.0817,0.7223</t>
-  </si>
-  <si>
-    <t>0.0057,0.9495,0.2062,0.0249</t>
-  </si>
-  <si>
-    <t>0.0022,0.9886,0.0180,0.0016</t>
-  </si>
-  <si>
-    <t>0.4020,0.4312,0.1932,0.0073</t>
-  </si>
-  <si>
-    <t>0.0002,0.9592,0.9426,0.0003</t>
-  </si>
-  <si>
-    <t>0.0296,0.9695,0.0075,0.0003</t>
-  </si>
-  <si>
-    <t>0.7016,0.3528,0.0277,0.0020</t>
-  </si>
-  <si>
-    <t>0.6081,0.5537,0.0129,0.0026</t>
-  </si>
-  <si>
-    <t>0.9870,0.0097,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.9863,0.0035,0.0020,0.0018</t>
-  </si>
-  <si>
-    <t>0.9877,0.0024,0.0022,0.0020</t>
-  </si>
-  <si>
-    <t>0.9495,0.0366,0.0093,0.0034</t>
-  </si>
-  <si>
-    <t>0.9936,0.0011,0.0036,0.0006</t>
-  </si>
-  <si>
-    <t>0.9941,0.0026,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9742,0.0079,0.0181,0.0017</t>
-  </si>
-  <si>
-    <t>0.9881,0.0047,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.0011,0.4700,0.9682,0.0005</t>
-  </si>
-  <si>
-    <t>0.0019,0.7321,0.7871,0.0001</t>
-  </si>
-  <si>
-    <t>0.0179,0.1483,0.8691,0.0189</t>
-  </si>
-  <si>
-    <t>0.0361,0.1104,0.9021,0.0023</t>
-  </si>
-  <si>
-    <t>0.4969,0.1210,0.4163,0.0476</t>
-  </si>
-  <si>
-    <t>0.2778,0.6574,0.0525,0.0219</t>
-  </si>
-  <si>
-    <t>0.7795,0.0182,0.3099,0.0058</t>
-  </si>
-  <si>
-    <t>0.6563,0.0885,0.2580,0.0157</t>
-  </si>
-  <si>
-    <t>0.0139,0.0006,0.0015,0.9939</t>
-  </si>
-  <si>
-    <t>0.0002,0.0052,0.0012,0.9994</t>
-  </si>
-  <si>
-    <t>0.0013,0.0016,0.0016,0.9984</t>
-  </si>
-  <si>
-    <t>0.0072,0.0007,0.0007,0.9967</t>
-  </si>
-  <si>
-    <t>0.0021,0.8389,0.8891,0.0007</t>
-  </si>
-  <si>
-    <t>0.9574,0.0381,0.0085,0.0015</t>
-  </si>
-  <si>
-    <t>0.1633,0.8269,0.0040,0.0145</t>
-  </si>
-  <si>
-    <t>0.9945,0.0008,0.0002,0.0010</t>
-  </si>
-  <si>
-    <t>0.7034,0.4808,0.0011,0.0007</t>
-  </si>
-  <si>
-    <t>0.9900,0.0005,0.0001,0.0050</t>
-  </si>
-  <si>
-    <t>0.3314,0.0114,0.0128,0.7909</t>
-  </si>
-  <si>
-    <t>0.9535,0.0180,0.0193,0.0044</t>
-  </si>
-  <si>
-    <t>0.0046,0.0546,0.9628,0.0327</t>
-  </si>
-  <si>
-    <t>0.4481,0.0009,0.0113,0.6231</t>
-  </si>
-  <si>
-    <t>0.6146,0.0009,0.0143,0.3429</t>
-  </si>
-  <si>
-    <t>0.3582,0.6775,0.0182,0.0053</t>
-  </si>
-  <si>
-    <t>0.7875,0.2240,0.0170,0.0088</t>
-  </si>
-  <si>
-    <t>0.9168,0.0280,0.0370,0.0039</t>
-  </si>
-  <si>
-    <t>0.6995,0.1846,0.1112,0.0265</t>
-  </si>
-  <si>
-    <t>0.8642,0.0714,0.0532,0.0085</t>
-  </si>
-  <si>
-    <t>0.9116,0.0653,0.0111,0.0050</t>
-  </si>
-  <si>
-    <t>0.9920,0.0012,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.9580,0.0067,0.0076,0.0123</t>
-  </si>
-  <si>
-    <t>0.9931,0.0031,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9945,0.0002,0.0002,0.0019</t>
-  </si>
-  <si>
-    <t>0.9400,0.0479,0.0087,0.0048</t>
-  </si>
-  <si>
-    <t>0.9876,0.0095,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9945,0.0034,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9867,0.0011,0.0002,0.0057</t>
-  </si>
-  <si>
-    <t>0.3641,0.6966,0.0144,0.0075</t>
-  </si>
-  <si>
-    <t>0.7682,0.3337,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.7708,0.3060,0.0018,0.0024</t>
-  </si>
-  <si>
-    <t>0.2951,0.6112,0.1883,0.0090</t>
-  </si>
-  <si>
-    <t>0.9535,0.0809,0.0017,0.0003</t>
-  </si>
-  <si>
-    <t>0.9604,0.0197,0.0143,0.0010</t>
-  </si>
-  <si>
-    <t>0.9486,0.0977,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.8572,0.1264,0.0296,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.0244,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.9671,0.0184,0.0073,0.0018</t>
-  </si>
-  <si>
-    <t>0.0033,0.0120,0.9902,0.0004</t>
-  </si>
-  <si>
-    <t>0.0048,0.3093,0.9532,0.0038</t>
-  </si>
-  <si>
-    <t>0.0140,0.0079,0.9807,0.0012</t>
-  </si>
-  <si>
-    <t>0.0028,0.0586,0.9789,0.0031</t>
-  </si>
-  <si>
-    <t>0.0110,0.0334,0.9684,0.0024</t>
-  </si>
-  <si>
-    <t>0.0022,0.0053,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0362,0.0117,0.9633,0.0029</t>
-  </si>
-  <si>
-    <t>0.5588,0.0650,0.4475,0.0037</t>
-  </si>
-  <si>
-    <t>0.0908,0.0165,0.9267,0.0021</t>
-  </si>
-  <si>
-    <t>0.7412,0.0105,0.3989,0.0030</t>
-  </si>
-  <si>
-    <t>0.1679,0.2841,0.5439,0.0306</t>
-  </si>
-  <si>
-    <t>0.1077,0.5162,0.3408,0.0029</t>
-  </si>
-  <si>
-    <t>0.6056,0.0165,0.5500,0.0011</t>
-  </si>
-  <si>
-    <t>0.2827,0.2811,0.5003,0.0290</t>
-  </si>
-  <si>
-    <t>0.1503,0.2691,0.5464,0.0032</t>
-  </si>
-  <si>
-    <t>0.9114,0.1680,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.7265,0.5071,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9678,0.0449,0.0013,0.0007</t>
-  </si>
-  <si>
-    <t>0.4668,0.6886,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.8534,0.2252,0.0078,0.0011</t>
-  </si>
-  <si>
-    <t>0.4085,0.5125,0.0905,0.0146</t>
-  </si>
-  <si>
-    <t>0.9186,0.0075,0.0442,0.0047</t>
-  </si>
-  <si>
-    <t>0.8394,0.0060,0.0812,0.0273</t>
-  </si>
-  <si>
-    <t>0.6856,0.0064,0.3469,0.0222</t>
-  </si>
-  <si>
-    <t>0.7834,0.0236,0.2566,0.0059</t>
-  </si>
-  <si>
-    <t>0.0364,0.0577,0.9267,0.0055</t>
-  </si>
-  <si>
-    <t>0.0096,0.8282,0.7852,0.0069</t>
-  </si>
-  <si>
-    <t>0.0423,0.1916,0.8665,0.0274</t>
-  </si>
-  <si>
-    <t>0.1561,0.0454,0.8208,0.0056</t>
-  </si>
-  <si>
-    <t>0.0018,0.5085,0.9399,0.0011</t>
-  </si>
-  <si>
-    <t>0.9944,0.0013,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9769,0.0249,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.9860,0.0190,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.9901,0.0049,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9486,0.0839,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0015,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9948,0.0031,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9911,0.0022,0.0006,0.0015</t>
-  </si>
-  <si>
-    <t>0.0667,0.0263,0.9225,0.0102</t>
-  </si>
-  <si>
-    <t>0.2649,0.6040,0.2075,0.0115</t>
-  </si>
-  <si>
-    <t>0.9125,0.0199,0.0555,0.0079</t>
-  </si>
-  <si>
-    <t>0.0079,0.0174,0.9836,0.0013</t>
-  </si>
-  <si>
-    <t>0.0015,0.0151,0.9926,0.0010</t>
-  </si>
-  <si>
-    <t>0.0064,0.1274,0.9544,0.0012</t>
-  </si>
-  <si>
-    <t>0.0027,0.0176,0.9941,0.0004</t>
-  </si>
-  <si>
-    <t>0.0630,0.0714,0.8581,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.0106,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0053,0.2209,0.9406,0.0023</t>
-  </si>
-  <si>
-    <t>0.0245,0.1243,0.9268,0.0028</t>
-  </si>
-  <si>
-    <t>0.6104,0.0341,0.4463,0.0102</t>
-  </si>
-  <si>
-    <t>0.8157,0.0125,0.2283,0.0040</t>
-  </si>
-  <si>
-    <t>0.7992,0.0006,0.1620,0.0218</t>
-  </si>
-  <si>
-    <t>0.9855,0.0133,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9970,0.0033,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0030,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9794,0.0122,0.0023,0.0016</t>
-  </si>
-  <si>
-    <t>0.9821,0.0095,0.0003,0.0018</t>
-  </si>
-  <si>
-    <t>0.9913,0.0114,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9954,0.0032,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9932,0.0037,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0120,0.0733,0.9368,0.0017</t>
-  </si>
-  <si>
-    <t>0.0017,0.4657,0.9512,0.0007</t>
-  </si>
-  <si>
-    <t>0.0086,0.0942,0.9526,0.0006</t>
-  </si>
-  <si>
-    <t>0.0664,0.1282,0.6534,0.0005</t>
-  </si>
-  <si>
-    <t>0.0030,0.0022,0.9683,0.0456</t>
-  </si>
-  <si>
-    <t>0.0657,0.0430,0.2225,0.8315</t>
-  </si>
-  <si>
-    <t>0.0422,0.0146,0.9342,0.0072</t>
-  </si>
-  <si>
-    <t>0.0572,0.1143,0.8494,0.0490</t>
-  </si>
-  <si>
-    <t>0.9320,0.0005,0.0024,0.0571</t>
-  </si>
-  <si>
-    <t>0.0132,0.1752,0.0020,0.9719</t>
-  </si>
-  <si>
-    <t>0.2229,0.0008,0.0017,0.9234</t>
-  </si>
-  <si>
-    <t>0.0056,0.0001,0.0015,0.9963</t>
-  </si>
-  <si>
-    <t>0.0051,0.0003,0.0001,0.9981</t>
-  </si>
-  <si>
-    <t>0.8385,0.0192,0.0060,0.0886</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.3221,0.0450,0.0847,0.6746</t>
+  </si>
+  <si>
+    <t>0.0252,0.0040,0.0031,0.9865</t>
+  </si>
+  <si>
+    <t>0.5347,0.0497,0.0060,0.4516</t>
+  </si>
+  <si>
+    <t>0.2637,0.0070,0.0060,0.8770</t>
+  </si>
+  <si>
+    <t>0.9975,0.0003,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9933,0.0034,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9892,0.0027,0.0002,0.0018</t>
+  </si>
+  <si>
+    <t>0.9957,0.0007,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9934,0.0038,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9926,0.0043,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9966,0.0006,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.4222,0.3371,0.3304,0.0225</t>
+  </si>
+  <si>
+    <t>0.0951,0.0610,0.8484,0.0034</t>
+  </si>
+  <si>
+    <t>0.2566,0.0025,0.8995,0.0006</t>
+  </si>
+  <si>
+    <t>0.0607,0.1057,0.7555,0.0021</t>
+  </si>
+  <si>
+    <t>0.8051,0.0049,0.2652,0.0110</t>
+  </si>
+  <si>
+    <t>0.2943,0.8188,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.0747,0.9422,0.0013,0.0004</t>
+  </si>
+  <si>
+    <t>0.7732,0.3547,0.0057,0.0014</t>
+  </si>
+  <si>
+    <t>0.5426,0.6631,0.0006,0.0008</t>
+  </si>
+  <si>
+    <t>0.0209,0.9726,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.7799,0.0051,0.2812,0.0066</t>
+  </si>
+  <si>
+    <t>0.3859,0.0264,0.6736,0.0184</t>
+  </si>
+  <si>
+    <t>0.0156,0.0989,0.9327,0.0146</t>
+  </si>
+  <si>
+    <t>0.1255,0.0045,0.8915,0.0142</t>
+  </si>
+  <si>
+    <t>0.0545,0.0240,0.9485,0.0031</t>
+  </si>
+  <si>
+    <t>0.1061,0.0113,0.8965,0.0077</t>
+  </si>
+  <si>
+    <t>0.0199,0.0040,0.9620,0.0079</t>
+  </si>
+  <si>
+    <t>0.4845,0.6158,0.0041,0.0003</t>
+  </si>
+  <si>
+    <t>0.1204,0.2165,0.6825,0.0044</t>
+  </si>
+  <si>
+    <t>0.0123,0.0054,0.9856,0.0003</t>
+  </si>
+  <si>
+    <t>0.0187,0.6266,0.3698,0.0013</t>
+  </si>
+  <si>
+    <t>0.5894,0.3664,0.0169,0.0238</t>
+  </si>
+  <si>
+    <t>0.4849,0.5209,0.0686,0.0101</t>
+  </si>
+  <si>
+    <t>0.7754,0.3142,0.0150,0.0024</t>
+  </si>
+  <si>
+    <t>0.0119,0.9764,0.0224,0.0023</t>
+  </si>
+  <si>
+    <t>0.0052,0.6858,0.2339,0.1406</t>
+  </si>
+  <si>
+    <t>0.2009,0.1159,0.7617,0.0132</t>
+  </si>
+  <si>
+    <t>0.0422,0.0912,0.8474,0.0486</t>
+  </si>
+  <si>
+    <t>0.1896,0.0171,0.5270,0.2608</t>
+  </si>
+  <si>
+    <t>0.0079,0.2343,0.9559,0.0016</t>
+  </si>
+  <si>
+    <t>0.0230,0.8983,0.0673,0.0012</t>
+  </si>
+  <si>
+    <t>0.0098,0.0691,0.9610,0.0021</t>
+  </si>
+  <si>
+    <t>0.2230,0.3068,0.0484,0.5752</t>
+  </si>
+  <si>
+    <t>0.0051,0.9815,0.0279,0.0036</t>
+  </si>
+  <si>
+    <t>0.0004,0.9965,0.0102,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.9899,0.0486,0.0023</t>
+  </si>
+  <si>
+    <t>0.0072,0.5230,0.9430,0.0064</t>
+  </si>
+  <si>
+    <t>0.0003,0.0333,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0184,0.0063,0.9671,0.0086</t>
+  </si>
+  <si>
+    <t>0.0183,0.0112,0.9800,0.0011</t>
+  </si>
+  <si>
+    <t>0.0006,0.0055,0.9929,0.0044</t>
+  </si>
+  <si>
+    <t>0.0030,0.0631,0.9793,0.0001</t>
+  </si>
+  <si>
+    <t>0.9732,0.0265,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9898,0.0016,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9746,0.0085,0.0016,0.0048</t>
+  </si>
+  <si>
+    <t>0.0056,0.0257,0.9830,0.0027</t>
+  </si>
+  <si>
+    <t>0.9895,0.0091,0.0006,0.0004</t>
+  </si>
+  <si>
+    <t>0.9938,0.0006,0.0000,0.0018</t>
+  </si>
+  <si>
+    <t>0.9706,0.0393,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.0068,0.6739,0.9239,0.0016</t>
+  </si>
+  <si>
+    <t>0.0043,0.0930,0.9793,0.0027</t>
+  </si>
+  <si>
+    <t>0.0106,0.0931,0.9391,0.0054</t>
+  </si>
+  <si>
+    <t>0.0002,0.9024,0.9804,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0035,0.9891,0.0026</t>
+  </si>
+  <si>
+    <t>0.0667,0.6699,0.2729,0.0026</t>
+  </si>
+  <si>
+    <t>0.0105,0.9879,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9102,0.0179,0.0741,0.0073</t>
+  </si>
+  <si>
+    <t>0.8733,0.0582,0.0811,0.0033</t>
+  </si>
+  <si>
+    <t>0.0197,0.0782,0.9554,0.0027</t>
+  </si>
+  <si>
+    <t>0.0024,0.9262,0.6942,0.0003</t>
+  </si>
+  <si>
+    <t>0.0004,0.8639,0.9357,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9928,0.0295,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9440,0.9284,0.0000</t>
+  </si>
+  <si>
+    <t>0.1021,0.0039,0.0370,0.9114</t>
+  </si>
+  <si>
+    <t>0.0035,0.0023,0.0003,0.9981</t>
+  </si>
+  <si>
+    <t>0.0019,0.0063,0.0015,0.9976</t>
+  </si>
+  <si>
+    <t>0.0129,0.0017,0.0006,0.9943</t>
+  </si>
+  <si>
+    <t>0.0500,0.0159,0.0130,0.9690</t>
+  </si>
+  <si>
+    <t>0.0165,0.0017,0.0009,0.9926</t>
+  </si>
+  <si>
+    <t>0.0007,0.9745,0.6079,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.8386,0.9757,0.0001</t>
+  </si>
+  <si>
+    <t>0.0335,0.4109,0.8295,0.0085</t>
+  </si>
+  <si>
+    <t>0.0066,0.3490,0.9487,0.0017</t>
+  </si>
+  <si>
+    <t>0.0005,0.8921,0.8575,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.8221,0.8737,0.0002</t>
+  </si>
+  <si>
+    <t>0.9861,0.0124,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.9812,0.0442,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9952,0.0043,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0016,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9921,0.0083,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0010,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9875,0.0053,0.0004,0.0015</t>
+  </si>
+  <si>
+    <t>0.9912,0.0090,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9976,0.0003,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9951,0.0009,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9984,0.0001,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9962,0.0007,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9978,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9969,0.0004,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.0135,0.9931,0.0004</t>
+  </si>
+  <si>
+    <t>0.0211,0.0125,0.9609,0.0041</t>
+  </si>
+  <si>
+    <t>0.5296,0.0270,0.5103,0.0207</t>
+  </si>
+  <si>
+    <t>0.0535,0.0074,0.9615,0.0007</t>
+  </si>
+  <si>
+    <t>0.0755,0.9333,0.0018,0.0005</t>
+  </si>
+  <si>
+    <t>0.1657,0.8782,0.0066,0.0015</t>
+  </si>
+  <si>
+    <t>0.0774,0.9107,0.0007,0.0041</t>
+  </si>
+  <si>
+    <t>0.7846,0.3816,0.0026,0.0007</t>
+  </si>
+  <si>
+    <t>0.0269,0.9589,0.0030,0.0058</t>
+  </si>
+  <si>
+    <t>0.0960,0.8900,0.0028,0.0044</t>
+  </si>
+  <si>
+    <t>0.8302,0.2567,0.0046,0.0015</t>
+  </si>
+  <si>
+    <t>0.6777,0.0170,0.4290,0.0090</t>
+  </si>
+  <si>
+    <t>0.1999,0.0185,0.8397,0.0087</t>
+  </si>
+  <si>
+    <t>0.5351,0.0835,0.3207,0.0828</t>
+  </si>
+  <si>
+    <t>0.3027,0.1490,0.5284,0.0023</t>
+  </si>
+  <si>
+    <t>0.1585,0.3103,0.0663,0.7960</t>
+  </si>
+  <si>
+    <t>0.0038,0.9858,0.0626,0.0025</t>
+  </si>
+  <si>
+    <t>0.0048,0.9836,0.0115,0.0004</t>
+  </si>
+  <si>
+    <t>0.0166,0.9068,0.0378,0.1993</t>
+  </si>
+  <si>
+    <t>0.0001,0.9773,0.8588,0.0002</t>
+  </si>
+  <si>
+    <t>0.0789,0.9460,0.0042,0.0008</t>
+  </si>
+  <si>
+    <t>0.9042,0.1597,0.0040,0.0009</t>
+  </si>
+  <si>
+    <t>0.4874,0.6043,0.0017,0.0055</t>
+  </si>
+  <si>
+    <t>0.9895,0.0121,0.0015,0.0003</t>
+  </si>
+  <si>
+    <t>0.9911,0.0008,0.0003,0.0032</t>
+  </si>
+  <si>
+    <t>0.9852,0.0136,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.9785,0.0193,0.0019,0.0007</t>
+  </si>
+  <si>
+    <t>0.9894,0.0086,0.0025,0.0002</t>
+  </si>
+  <si>
+    <t>0.9798,0.0237,0.0043,0.0002</t>
+  </si>
+  <si>
+    <t>0.9652,0.0183,0.0048,0.0048</t>
+  </si>
+  <si>
+    <t>0.9788,0.0115,0.0049,0.0014</t>
+  </si>
+  <si>
+    <t>0.0066,0.5614,0.9409,0.0013</t>
+  </si>
+  <si>
+    <t>0.0068,0.6154,0.7577,0.0006</t>
+  </si>
+  <si>
+    <t>0.0146,0.3661,0.8083,0.0009</t>
+  </si>
+  <si>
+    <t>0.0740,0.2531,0.6186,0.0013</t>
+  </si>
+  <si>
+    <t>0.6092,0.0843,0.3612,0.0390</t>
+  </si>
+  <si>
+    <t>0.5350,0.2950,0.1495,0.0234</t>
+  </si>
+  <si>
+    <t>0.7190,0.0056,0.3992,0.0106</t>
+  </si>
+  <si>
+    <t>0.3412,0.4473,0.1390,0.0029</t>
+  </si>
+  <si>
+    <t>0.1996,0.0018,0.0016,0.9315</t>
+  </si>
+  <si>
+    <t>0.0003,0.0028,0.0002,0.9995</t>
+  </si>
+  <si>
+    <t>0.0012,0.0343,0.0019,0.9973</t>
+  </si>
+  <si>
+    <t>0.0216,0.0010,0.0017,0.9908</t>
+  </si>
+  <si>
+    <t>0.0008,0.9656,0.2620,0.0000</t>
+  </si>
+  <si>
+    <t>0.9739,0.0298,0.0039,0.0004</t>
+  </si>
+  <si>
+    <t>0.2773,0.7242,0.0025,0.0138</t>
+  </si>
+  <si>
+    <t>0.9268,0.0323,0.0002,0.0078</t>
+  </si>
+  <si>
+    <t>0.5146,0.6279,0.0051,0.0006</t>
+  </si>
+  <si>
+    <t>0.9657,0.0147,0.0151,0.0021</t>
+  </si>
+  <si>
+    <t>0.5447,0.0138,0.0035,0.5598</t>
+  </si>
+  <si>
+    <t>0.9544,0.0358,0.0101,0.0021</t>
+  </si>
+  <si>
+    <t>0.0002,0.2505,0.9807,0.0084</t>
+  </si>
+  <si>
+    <t>0.7910,0.0079,0.0188,0.1406</t>
+  </si>
+  <si>
+    <t>0.9122,0.0043,0.0030,0.0658</t>
+  </si>
+  <si>
+    <t>0.7865,0.2919,0.0036,0.0025</t>
+  </si>
+  <si>
+    <t>0.9332,0.0443,0.0068,0.0025</t>
+  </si>
+  <si>
+    <t>0.8449,0.1009,0.0548,0.0049</t>
+  </si>
+  <si>
+    <t>0.1653,0.7601,0.0060,0.0378</t>
+  </si>
+  <si>
+    <t>0.8119,0.0412,0.2078,0.0017</t>
+  </si>
+  <si>
+    <t>0.8140,0.1686,0.0555,0.0055</t>
+  </si>
+  <si>
+    <t>0.9953,0.0036,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9833,0.0048,0.0016,0.0028</t>
+  </si>
+  <si>
+    <t>0.9925,0.0022,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9887,0.0022,0.0008,0.0022</t>
+  </si>
+  <si>
+    <t>0.9818,0.0019,0.0007,0.0080</t>
+  </si>
+  <si>
+    <t>0.9706,0.0199,0.0109,0.0006</t>
+  </si>
+  <si>
+    <t>0.9824,0.0075,0.0021,0.0016</t>
+  </si>
+  <si>
+    <t>0.9892,0.0028,0.0012,0.0019</t>
+  </si>
+  <si>
+    <t>0.7879,0.2713,0.0158,0.0118</t>
+  </si>
+  <si>
+    <t>0.4942,0.5492,0.0370,0.0017</t>
+  </si>
+  <si>
+    <t>0.3125,0.7748,0.0052,0.0022</t>
+  </si>
+  <si>
+    <t>0.9282,0.0439,0.0307,0.0051</t>
+  </si>
+  <si>
+    <t>0.9675,0.0444,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.8673,0.1360,0.0102,0.0062</t>
+  </si>
+  <si>
+    <t>0.9701,0.0417,0.0025,0.0003</t>
+  </si>
+  <si>
+    <t>0.9645,0.0226,0.0141,0.0027</t>
+  </si>
+  <si>
+    <t>0.0007,0.0305,0.9970,0.0003</t>
+  </si>
+  <si>
+    <t>0.9589,0.0432,0.0083,0.0006</t>
+  </si>
+  <si>
+    <t>0.0157,0.0443,0.9683,0.0018</t>
+  </si>
+  <si>
+    <t>0.0032,0.3281,0.9695,0.0019</t>
+  </si>
+  <si>
+    <t>0.0828,0.0111,0.9336,0.0027</t>
+  </si>
+  <si>
+    <t>0.0170,0.1277,0.9449,0.0018</t>
+  </si>
+  <si>
+    <t>0.0179,0.0064,0.9872,0.0003</t>
+  </si>
+  <si>
+    <t>0.0158,0.0017,0.9886,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.0032,0.9829,0.0025</t>
+  </si>
+  <si>
+    <t>0.3953,0.0350,0.6721,0.0039</t>
+  </si>
+  <si>
+    <t>0.1120,0.0466,0.8623,0.0106</t>
+  </si>
+  <si>
+    <t>0.7866,0.0203,0.1763,0.0288</t>
+  </si>
+  <si>
+    <t>0.2620,0.1827,0.5324,0.0094</t>
+  </si>
+  <si>
+    <t>0.2999,0.1112,0.6095,0.0059</t>
+  </si>
+  <si>
+    <t>0.2709,0.4099,0.3428,0.0099</t>
+  </si>
+  <si>
+    <t>0.4714,0.0885,0.4285,0.0877</t>
+  </si>
+  <si>
+    <t>0.0722,0.8400,0.0678,0.0239</t>
+  </si>
+  <si>
+    <t>0.7652,0.3938,0.0031,0.0003</t>
+  </si>
+  <si>
+    <t>0.8781,0.3119,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9088,0.1451,0.0036,0.0006</t>
+  </si>
+  <si>
+    <t>0.9852,0.0128,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9194,0.1311,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.3722,0.4832,0.1329,0.0302</t>
+  </si>
+  <si>
+    <t>0.8028,0.0063,0.3012,0.0058</t>
+  </si>
+  <si>
+    <t>0.7300,0.0225,0.1554,0.0483</t>
+  </si>
+  <si>
+    <t>0.5817,0.0071,0.5072,0.0124</t>
+  </si>
+  <si>
+    <t>0.8766,0.0163,0.1290,0.0025</t>
+  </si>
+  <si>
+    <t>0.2009,0.0354,0.7905,0.0129</t>
+  </si>
+  <si>
+    <t>0.0053,0.1853,0.9588,0.0097</t>
+  </si>
+  <si>
+    <t>0.0029,0.2566,0.9727,0.0007</t>
+  </si>
+  <si>
+    <t>0.1444,0.0573,0.8142,0.0295</t>
+  </si>
+  <si>
+    <t>0.0051,0.4623,0.8912,0.0034</t>
+  </si>
+  <si>
+    <t>0.9925,0.0032,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9647,0.0362,0.0086,0.0011</t>
+  </si>
+  <si>
+    <t>0.9910,0.0074,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9918,0.0044,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9851,0.0177,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9949,0.0055,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9921,0.0024,0.0002,0.0010</t>
+  </si>
+  <si>
+    <t>0.9811,0.0088,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.0092,0.0082,0.9896,0.0004</t>
+  </si>
+  <si>
+    <t>0.0536,0.7539,0.3026,0.0031</t>
+  </si>
+  <si>
+    <t>0.7095,0.0474,0.2544,0.0256</t>
+  </si>
+  <si>
+    <t>0.0069,0.0088,0.9921,0.0002</t>
+  </si>
+  <si>
+    <t>0.0018,0.0282,0.9882,0.0020</t>
+  </si>
+  <si>
+    <t>0.0243,0.0815,0.9351,0.0049</t>
+  </si>
+  <si>
+    <t>0.0017,0.0082,0.9948,0.0010</t>
+  </si>
+  <si>
+    <t>0.1990,0.0229,0.8332,0.0066</t>
+  </si>
+  <si>
+    <t>0.0061,0.2003,0.9727,0.0027</t>
+  </si>
+  <si>
+    <t>0.0099,0.0647,0.9722,0.0006</t>
+  </si>
+  <si>
+    <t>0.1547,0.0596,0.8098,0.0093</t>
+  </si>
+  <si>
+    <t>0.7617,0.0066,0.2384,0.0276</t>
+  </si>
+  <si>
+    <t>0.6920,0.0166,0.3658,0.0130</t>
+  </si>
+  <si>
+    <t>0.6646,0.0048,0.4771,0.0114</t>
+  </si>
+  <si>
+    <t>0.9884,0.0082,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0006,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9927,0.0082,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9829,0.0265,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.9720,0.0314,0.0010,0.0011</t>
+  </si>
+  <si>
+    <t>0.9914,0.0066,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9967,0.0020,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0127,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0084,0.4002,0.6876,0.0019</t>
+  </si>
+  <si>
+    <t>0.0010,0.1437,0.9902,0.0008</t>
+  </si>
+  <si>
+    <t>0.0095,0.2128,0.8931,0.0008</t>
+  </si>
+  <si>
+    <t>0.0653,0.0632,0.8456,0.0094</t>
+  </si>
+  <si>
+    <t>0.0020,0.0007,0.9956,0.0011</t>
+  </si>
+  <si>
+    <t>0.0488,0.0570,0.2513,0.8504</t>
+  </si>
+  <si>
+    <t>0.1229,0.0104,0.8927,0.0094</t>
+  </si>
+  <si>
+    <t>0.0703,0.1114,0.7788,0.0990</t>
+  </si>
+  <si>
+    <t>0.2975,0.0004,0.0018,0.8796</t>
+  </si>
+  <si>
+    <t>0.0134,0.2228,0.0024,0.9736</t>
+  </si>
+  <si>
+    <t>0.0529,0.0031,0.0009,0.9826</t>
+  </si>
+  <si>
+    <t>0.0167,0.0009,0.0003,0.9949</t>
+  </si>
+  <si>
+    <t>0.0047,0.0017,0.0011,0.9962</t>
+  </si>
+  <si>
+    <t>0.8438,0.0535,0.0234,0.0323</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1965,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2133,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2233,10 +2245,10 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2290,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2388,7 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2525,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2637,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,10 +2805,10 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3130,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>275</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3659,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4642,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4751,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,7 +5048,7 @@
         <v>262</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5412,7 @@
         <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
